--- a/front/public/excel/salesSheetTemplate.xlsx
+++ b/front/public/excel/salesSheetTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b25a0186\Desktop\販管Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE35966-1344-41E0-BD90-99A6C34916F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E2EF2D-1925-414C-8A2C-A0C140179B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-7125" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="売上一覧" sheetId="1" r:id="rId1"/>
@@ -253,14 +253,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -554,11 +554,12 @@
     <col min="2" max="2" width="18.58203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="16.4140625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="21.58203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="18.25" customWidth="1"/>
+    <col min="6" max="6" width="12.58203125" customWidth="1"/>
+    <col min="7" max="7" width="16.5" style="7" customWidth="1"/>
+    <col min="8" max="8" width="20.5" style="7" customWidth="1"/>
     <col min="9" max="9" width="20.4140625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="19.1640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -567,10 +568,10 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8"/>
+      <c r="I1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:11" ht="18.5" thickBot="1">
       <c r="A2" s="2"/>
@@ -578,11 +579,11 @@
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="36" thickTop="1" thickBot="1">
@@ -593,11 +594,11 @@
       <c r="C3" s="11"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="22.5" thickTop="1">
@@ -606,11 +607,11 @@
       <c r="C4" s="4"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
@@ -619,11 +620,11 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="22.5" thickBot="1">
@@ -633,10 +634,10 @@
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="1"/>
-      <c r="H6" s="10" t="s">
+      <c r="I6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="10">
+      <c r="J6" s="9">
         <v>0</v>
       </c>
     </row>
@@ -646,11 +647,11 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
       <c r="K7" s="1"/>
     </row>
   </sheetData>

--- a/front/public/excel/salesSheetTemplate.xlsx
+++ b/front/public/excel/salesSheetTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b25a0186\Desktop\販管Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E2EF2D-1925-414C-8A2C-A0C140179B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD4252-4742-48ED-B7E1-79349AC3690D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -232,7 +232,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
@@ -264,6 +264,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -547,19 +551,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="18.25" customWidth="1"/>
-    <col min="6" max="6" width="12.58203125" customWidth="1"/>
-    <col min="7" max="7" width="16.5" style="7" customWidth="1"/>
-    <col min="8" max="8" width="20.5" style="7" customWidth="1"/>
-    <col min="9" max="9" width="20.4140625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="19.1640625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="17.4140625" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="12" customWidth="1"/>
+    <col min="8" max="9" width="21.25" style="7" customWidth="1"/>
+    <col min="10" max="10" width="21.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.25" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -569,7 +573,7 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="H1" s="8"/>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>3</v>
       </c>
     </row>
@@ -580,11 +584,11 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="8"/>
+      <c r="G2" s="13"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="K2" s="1"/>
+      <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11" ht="36" thickTop="1" thickBot="1">
       <c r="A3" s="11" t="s">
@@ -595,11 +599,11 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="8"/>
+      <c r="G3" s="13"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="1"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="1:11" ht="22.5" thickTop="1">
       <c r="A4" s="3"/>
@@ -608,11 +612,11 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="8"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="1"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1"/>
@@ -621,11 +625,11 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="8"/>
+      <c r="G5" s="13"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="1"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:11" ht="22.5" thickBot="1">
       <c r="A6" s="5" t="s">
@@ -634,10 +638,10 @@
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="1"/>
-      <c r="I6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="9">
+      <c r="K6" s="9">
         <v>0</v>
       </c>
     </row>
@@ -648,11 +652,39 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="8"/>
+      <c r="G7" s="13"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="1"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/front/public/excel/salesSheetTemplate.xlsx
+++ b/front/public/excel/salesSheetTemplate.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b25a0186\Desktop\販管Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcshd365.sharepoint.com/sites/msteams_e9d089-WG/Shared Documents/人材開発推進WG/30_新人教育/2025年度/販売管理システム/販売管理システムExcelテンプレート/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD4252-4742-48ED-B7E1-79349AC3690D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{9CFD4252-4742-48ED-B7E1-79349AC3690D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{537B6C7D-813C-41E7-8EA1-C48DC5274AE2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="売上一覧" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">OFFSET(売上一覧!$A$1,0,0,IF(ISBLANK(売上一覧!$A$8),8,COUNTA(売上一覧!$A$8:$A$1048536)+9),12)</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -92,7 +95,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
+    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0_);[Red]\(&quot;¥&quot;#,##0\)"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -252,23 +255,21 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -551,22 +552,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.4140625" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
-    <col min="3" max="3" width="17.08203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="12" customWidth="1"/>
-    <col min="8" max="9" width="21.25" style="7" customWidth="1"/>
-    <col min="10" max="10" width="21.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.25" style="7" customWidth="1"/>
+    <col min="1" max="1" width="17.4140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="34.08203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="34.08203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="7" customWidth="1"/>
+    <col min="8" max="9" width="21.25" style="9" customWidth="1"/>
+    <col min="10" max="10" width="21.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" ht="16">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -577,29 +579,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.5" thickBot="1">
+    <row r="2" spans="1:11" ht="15.5" thickBot="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="13"/>
+      <c r="G2" s="1"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11" ht="36" thickTop="1" thickBot="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="13"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
@@ -612,8 +614,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="1"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -625,7 +626,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="13"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -638,53 +639,29 @@
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="1"/>
-      <c r="J6" s="9" t="s">
+      <c r="H6" s="8"/>
+      <c r="J6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18.5" thickTop="1">
+    <row r="7" spans="1:11" ht="15.5" thickTop="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-    </row>
     <row r="9" spans="1:11">
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
+      <c r="A9" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -692,5 +669,245 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="29" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100531F82A73EE04949B92C893AA9ED3D8B" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9410a1db6c4108f6da538e5e9d46e9dc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18ad70a2-d0c6-4b98-b594-e1471017f0f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="554750112bcaa4f1e868a2b7404a37fc" ns2:_="">
+    <xsd:import namespace="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="18ad70a2-d0c6-4b98-b594-e1471017f0f2" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a6ccf9c2-98cb-4187-8406-2fdadecc4fdb" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18ad70a2-d0c6-4b98-b594-e1471017f0f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A23335A5-B950-485D-ADF2-F486BBCCD258}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5D936F6-E537-444C-A403-FC249B3159F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56C319EA-37A1-4EC7-A8FF-9855F426DA4F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/front/public/excel/salesSheetTemplate.xlsx
+++ b/front/public/excel/salesSheetTemplate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcshd365.sharepoint.com/sites/msteams_e9d089-WG/Shared Documents/人材開発推進WG/30_新人教育/2025年度/販売管理システム/販売管理システムExcelテンプレート/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b25a0186\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{9CFD4252-4742-48ED-B7E1-79349AC3690D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{537B6C7D-813C-41E7-8EA1-C48DC5274AE2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507931D6-A060-422F-8320-E1EFE7B0192E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6360" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-7125" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="売上一覧" sheetId="1" r:id="rId1"/>
@@ -266,10 +266,10 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -593,11 +593,11 @@
       <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11" ht="36" thickTop="1" thickBot="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -661,7 +661,7 @@
       <c r="K7" s="8"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="13"/>
+      <c r="A9" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -674,6 +674,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18ad70a2-d0c6-4b98-b594-e1471017f0f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100531F82A73EE04949B92C893AA9ED3D8B" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9410a1db6c4108f6da538e5e9d46e9dc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18ad70a2-d0c6-4b98-b594-e1471017f0f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="554750112bcaa4f1e868a2b7404a37fc" ns2:_="">
     <xsd:import namespace="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
@@ -851,26 +870,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18ad70a2-d0c6-4b98-b594-e1471017f0f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56C319EA-37A1-4EC7-A8FF-9855F426DA4F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5D936F6-E537-444C-A403-FC249B3159F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A23335A5-B950-485D-ADF2-F486BBCCD258}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -886,28 +910,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5D936F6-E537-444C-A403-FC249B3159F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56C319EA-37A1-4EC7-A8FF-9855F426DA4F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>